--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$B$1:$B$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$B$1:$B$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="116">
   <si>
     <t>序号</t>
   </si>
@@ -182,79 +182,82 @@
     <t>勇者大陆</t>
   </si>
   <si>
-    <t>仙踪林</t>
-  </si>
-  <si>
-    <t>幻术园</t>
-  </si>
-  <si>
-    <t>幻术园2</t>
-  </si>
-  <si>
-    <t>幻术园3</t>
-  </si>
-  <si>
-    <t>冰风谷</t>
-  </si>
-  <si>
-    <t>冰风谷2</t>
-  </si>
-  <si>
-    <t>冰风谷3</t>
-  </si>
-  <si>
-    <t>冰风谷4</t>
-  </si>
-  <si>
-    <t>地下城</t>
-  </si>
-  <si>
-    <t>地下城2</t>
-  </si>
-  <si>
-    <t>地下城3</t>
-  </si>
-  <si>
-    <t>失落之塔1</t>
-  </si>
-  <si>
-    <t>失落之塔2</t>
-  </si>
-  <si>
-    <t>失落之塔3</t>
-  </si>
-  <si>
-    <t>失落之塔4</t>
-  </si>
-  <si>
-    <t>失落之塔5</t>
-  </si>
-  <si>
-    <t>失落之塔6</t>
-  </si>
-  <si>
-    <t>失落之塔7</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯2</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯3</t>
-  </si>
-  <si>
-    <t>死亡沙漠</t>
-  </si>
-  <si>
-    <t>死亡沙漠2</t>
-  </si>
-  <si>
-    <t>幽暗森林</t>
-  </si>
-  <si>
-    <t>幽暗森林2</t>
+    <t xml:space="preserve">仙踪林  </t>
+  </si>
+  <si>
+    <t>幻术园一</t>
+  </si>
+  <si>
+    <t>幻术园二</t>
+  </si>
+  <si>
+    <t>幻术园三</t>
+  </si>
+  <si>
+    <t>冰风谷一</t>
+  </si>
+  <si>
+    <t>冰风谷二</t>
+  </si>
+  <si>
+    <t>冰风谷三</t>
+  </si>
+  <si>
+    <t>冰风谷四</t>
+  </si>
+  <si>
+    <t>地下城一</t>
+  </si>
+  <si>
+    <t>地下城二</t>
+  </si>
+  <si>
+    <t>地下城三</t>
+  </si>
+  <si>
+    <t>失落之塔一</t>
+  </si>
+  <si>
+    <t>失落之塔二</t>
+  </si>
+  <si>
+    <t>失落之塔三</t>
+  </si>
+  <si>
+    <t>失落之塔四</t>
+  </si>
+  <si>
+    <t>失落之塔五</t>
+  </si>
+  <si>
+    <t>失落之塔六</t>
+  </si>
+  <si>
+    <t>失落之塔七</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯一</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯二</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯三</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;99999</t>
+  </si>
+  <si>
+    <t>死亡沙漠一</t>
+  </si>
+  <si>
+    <t>死亡沙漠二</t>
+  </si>
+  <si>
+    <t>幽暗森林一</t>
+  </si>
+  <si>
+    <t>幽暗森林二</t>
   </si>
   <si>
     <t>天空之城</t>
@@ -263,52 +266,31 @@
     <t>checkWearEquip[14]&gt;0</t>
   </si>
   <si>
-    <t>坎特鲁废墟</t>
-  </si>
-  <si>
-    <t>坎特鲁废墟2</t>
-  </si>
-  <si>
-    <t>坎特鲁废墟3</t>
-  </si>
-  <si>
-    <t>坎特鲁遗址</t>
-  </si>
-  <si>
-    <t>坎特鲁遗址2</t>
-  </si>
-  <si>
-    <t>冰霜之城</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>冰霜之城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>冰霜之城3</t>
+    <t>坎特鲁废墟一</t>
+  </si>
+  <si>
+    <t>坎特鲁废墟二</t>
+  </si>
+  <si>
+    <t>坎特鲁遗址一</t>
+  </si>
+  <si>
+    <t>坎特鲁遗址二</t>
+  </si>
+  <si>
+    <t>冰霜之城一</t>
+  </si>
+  <si>
+    <t>冰霜之城二</t>
+  </si>
+  <si>
+    <t>冰霜之城三</t>
   </si>
   <si>
     <t>安宁池</t>
   </si>
   <si>
     <t>恶魔广场1</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;99999</t>
   </si>
   <si>
     <t>恶魔广场2</t>
@@ -1493,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1774,7 +1756,7 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:15">
@@ -1807,7 +1789,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="O7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:15">
@@ -1836,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="O8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:15">
@@ -1865,7 +1847,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:15">
@@ -1902,7 +1884,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="O10" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:15">
@@ -1931,7 +1913,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:15">
@@ -1960,7 +1942,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:15">
@@ -1989,7 +1971,7 @@
         <v>2</v>
       </c>
       <c r="O13" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:15">
@@ -2027,7 +2009,7 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="O14" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:15">
@@ -2038,10 +2020,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>15</v>
@@ -2065,7 +2047,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="O15" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:15">
@@ -2076,10 +2058,10 @@
         <v>59</v>
       </c>
       <c r="C16" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D16" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>15</v>
@@ -2103,7 +2085,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="O16" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:15">
@@ -2114,10 +2096,10 @@
         <v>60</v>
       </c>
       <c r="C17" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>15</v>
@@ -2141,7 +2123,7 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="O17" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:15">
@@ -2152,10 +2134,10 @@
         <v>61</v>
       </c>
       <c r="C18" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D18" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>15</v>
@@ -2179,7 +2161,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="O18" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:15">
@@ -2190,10 +2172,10 @@
         <v>62</v>
       </c>
       <c r="C19" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>15</v>
@@ -2217,7 +2199,7 @@
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="O19" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:15">
@@ -2228,10 +2210,10 @@
         <v>63</v>
       </c>
       <c r="C20" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D20" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>15</v>
@@ -2255,7 +2237,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="O20" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:15">
@@ -2266,10 +2248,10 @@
         <v>64</v>
       </c>
       <c r="C21" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>15</v>
@@ -2293,7 +2275,7 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="O21" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:15">
@@ -2304,10 +2286,10 @@
         <v>65</v>
       </c>
       <c r="C22" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>15</v>
@@ -2331,7 +2313,7 @@
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="O22" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:15">
@@ -2342,10 +2324,10 @@
         <v>66</v>
       </c>
       <c r="C23" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>15</v>
@@ -2369,7 +2351,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="O23" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:15">
@@ -2408,7 +2390,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:15">
@@ -2447,7 +2429,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:15">
@@ -2480,13 +2462,13 @@
         <v>2</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:15">
@@ -2494,13 +2476,13 @@
         <v>17</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D27" s="9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>15</v>
@@ -2525,7 +2507,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:15">
@@ -2533,13 +2515,13 @@
         <v>17001</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D28" s="9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>15</v>
@@ -2564,7 +2546,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
@@ -2572,7 +2554,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1">
         <v>170</v>
@@ -2593,7 +2575,7 @@
         <v>2</v>
       </c>
       <c r="O29" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:15">
@@ -2601,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1">
         <v>170</v>
@@ -2622,7 +2604,7 @@
         <v>2</v>
       </c>
       <c r="O30" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:15">
@@ -2630,16 +2612,16 @@
         <v>21</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" s="9">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="D31" s="9">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F31" s="1">
         <v>1011</v>
@@ -2659,7 +2641,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:15">
@@ -2667,13 +2649,13 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="9">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D32" s="9">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="F32" s="1">
         <v>1038</v>
@@ -2695,7 +2677,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:15">
@@ -2703,13 +2685,13 @@
         <v>24001</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="9">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="D33" s="9">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="F33" s="1">
         <v>1038</v>
@@ -2731,178 +2713,182 @@
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:15">
-      <c r="A34" s="1">
-        <v>24002</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
+      <c r="A34" s="5">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C34" s="9">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="D34" s="9">
-        <v>250</v>
-      </c>
-      <c r="F34" s="1">
-        <v>103802</v>
-      </c>
-      <c r="G34" s="7">
-        <v>197</v>
-      </c>
-      <c r="H34" s="7">
-        <v>197</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1039</v>
+      </c>
+      <c r="G34" s="1">
+        <v>80</v>
+      </c>
+      <c r="H34" s="1">
+        <v>105</v>
+      </c>
+      <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:15">
-      <c r="A35" s="5">
-        <v>26</v>
+      <c r="A35" s="1">
+        <v>2601</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="9">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="D35" s="9">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="5">
-        <v>1039</v>
+      <c r="F35" s="1">
+        <v>103902</v>
       </c>
       <c r="G35" s="1">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H35" s="1">
-        <v>105</v>
-      </c>
-      <c r="I35" s="1"/>
+        <v>139</v>
+      </c>
       <c r="J35" s="1">
         <v>2</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
       <c r="O35" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:15">
-      <c r="A36" s="1">
-        <v>2601</v>
+      <c r="A36" s="5">
+        <v>28</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C36" s="9">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D36" s="9">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="1">
-        <v>103902</v>
+      <c r="F36" s="5">
+        <v>1058</v>
       </c>
       <c r="G36" s="1">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="H36" s="1">
-        <v>139</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="I36" s="1"/>
       <c r="J36" s="1">
         <v>2</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
       <c r="O36" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:15">
-      <c r="A37" s="5">
-        <v>28</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="15" spans="1:15">
+      <c r="A37" s="1">
+        <v>2801</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="9">
-        <v>330</v>
-      </c>
-      <c r="D37" s="9">
-        <v>330</v>
+        <v>82</v>
+      </c>
+      <c r="C37" s="1">
+        <v>300</v>
+      </c>
+      <c r="D37" s="1">
+        <v>300</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F37" s="5">
-        <v>1058</v>
-      </c>
-      <c r="G37" s="1">
-        <v>216</v>
-      </c>
-      <c r="H37" s="1">
-        <v>205</v>
-      </c>
-      <c r="I37" s="1"/>
+      <c r="F37" s="1">
+        <v>105802</v>
+      </c>
+      <c r="G37" s="7">
+        <v>101</v>
+      </c>
+      <c r="H37" s="7">
+        <v>209</v>
+      </c>
       <c r="J37" s="1">
         <v>2</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
+      <c r="M37" s="10"/>
       <c r="O37" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="15" spans="1:15">
       <c r="A38" s="1">
-        <v>2801</v>
+        <v>2802</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="1">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D38" s="1">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="1">
-        <v>105802</v>
+        <v>105803</v>
       </c>
       <c r="G38" s="7">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="H38" s="7">
-        <v>209</v>
+        <v>24</v>
       </c>
       <c r="J38" s="1">
         <v>2</v>
@@ -2912,33 +2898,30 @@
       </c>
       <c r="M38" s="10"/>
       <c r="O38" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="15" spans="1:15">
-      <c r="A39" s="1">
-        <v>2802</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>83</v>
+      <c r="A39" s="5">
+        <v>31</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="C39" s="1">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="D39" s="1">
-        <v>330</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="1">
-        <v>105803</v>
-      </c>
-      <c r="G39" s="7">
-        <v>194</v>
-      </c>
-      <c r="H39" s="7">
-        <v>24</v>
+        <v>350</v>
+      </c>
+      <c r="F39" s="5">
+        <v>1057</v>
+      </c>
+      <c r="G39" s="1">
+        <v>140</v>
+      </c>
+      <c r="H39" s="1">
+        <v>108</v>
       </c>
       <c r="J39" s="1">
         <v>2</v>
@@ -2946,52 +2929,55 @@
       <c r="K39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="10"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="1"/>
       <c r="O39" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="15" spans="1:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:15">
       <c r="A40" s="5">
-        <v>31</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="1">
-        <v>370</v>
-      </c>
-      <c r="D40" s="1">
-        <v>370</v>
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F40" s="5">
-        <v>1057</v>
+        <v>1010</v>
       </c>
       <c r="G40" s="1">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H40" s="1">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J40" s="1">
         <v>2</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" s="1"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="3">
-        <v>14</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O40" s="3"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -3003,16 +2989,16 @@
         <v>1010</v>
       </c>
       <c r="G41" s="1">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="H41" s="1">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J41" s="1">
         <v>2</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>15</v>
@@ -3024,7 +3010,7 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
       <c r="A42" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>87</v>
@@ -3039,16 +3025,16 @@
         <v>1010</v>
       </c>
       <c r="G42" s="1">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H42" s="1">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="J42" s="1">
         <v>2</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>15</v>
@@ -3060,7 +3046,7 @@
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
       <c r="A43" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>88</v>
@@ -3075,16 +3061,16 @@
         <v>1010</v>
       </c>
       <c r="G43" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H43" s="1">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="J43" s="1">
         <v>2</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>15</v>
@@ -3096,7 +3082,7 @@
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
       <c r="A44" s="5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>89</v>
@@ -3110,17 +3096,17 @@
       <c r="F44" s="5">
         <v>1010</v>
       </c>
-      <c r="G44" s="1">
-        <v>142</v>
-      </c>
-      <c r="H44" s="1">
-        <v>89</v>
+      <c r="G44" s="5">
+        <v>133</v>
+      </c>
+      <c r="H44" s="5">
+        <v>91</v>
       </c>
       <c r="J44" s="1">
         <v>2</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>15</v>
@@ -3132,7 +3118,7 @@
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
       <c r="A45" s="5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>90</v>
@@ -3147,16 +3133,16 @@
         <v>1010</v>
       </c>
       <c r="G45" s="5">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H45" s="5">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="J45" s="1">
         <v>2</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>15</v>
@@ -3168,7 +3154,7 @@
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
       <c r="A46" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>91</v>
@@ -3192,7 +3178,7 @@
         <v>2</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>15</v>
@@ -3204,7 +3190,7 @@
     </row>
     <row r="47" s="1" customFormat="1" spans="1:15">
       <c r="A47" s="5">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
@@ -3216,19 +3202,19 @@
         <v>15</v>
       </c>
       <c r="F47" s="5">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="G47" s="5">
-        <v>135</v>
+        <v>12</v>
       </c>
       <c r="H47" s="5">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="J47" s="1">
         <v>2</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>15</v>
@@ -3239,8 +3225,8 @@
       <c r="O47" s="3"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:15">
-      <c r="A48" s="5">
-        <v>55</v>
+      <c r="A48" s="1">
+        <v>16001</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>93</v>
@@ -3251,20 +3237,20 @@
       <c r="E48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F48" s="5">
-        <v>1012</v>
+      <c r="F48" s="1">
+        <v>16001</v>
       </c>
       <c r="G48" s="5">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="H48" s="5">
-        <v>5</v>
+        <v>209</v>
       </c>
       <c r="J48" s="1">
         <v>2</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>15</v>
@@ -3274,151 +3260,147 @@
       </c>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:15">
-      <c r="A49" s="1">
-        <v>16001</v>
-      </c>
-      <c r="B49" s="1" t="s">
+    <row r="49" customFormat="1" spans="1:15">
+      <c r="A49" s="5">
+        <v>33</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>94</v>
       </c>
+      <c r="C49" s="5">
+        <v>1</v>
+      </c>
       <c r="D49" s="5">
         <v>1</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="1">
-        <v>16001</v>
-      </c>
-      <c r="G49" s="5">
-        <v>87</v>
+      <c r="F49" s="5">
+        <v>1035</v>
+      </c>
+      <c r="G49" s="1">
+        <v>139</v>
       </c>
       <c r="H49" s="5">
-        <v>209</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I49" s="1"/>
       <c r="J49" s="1">
         <v>2</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" customFormat="1" spans="1:15">
+      <c r="M49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" ht="15" spans="1:15">
       <c r="A50" s="5">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="5">
-        <v>1</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5">
-        <v>1035</v>
+      <c r="C50" s="1">
+        <v>70</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="F50" s="13">
+        <v>10013</v>
       </c>
       <c r="G50" s="1">
-        <v>139</v>
-      </c>
-      <c r="H50" s="5">
-        <v>37</v>
-      </c>
-      <c r="I50" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="H50" s="1">
+        <v>80</v>
+      </c>
+      <c r="I50"/>
       <c r="J50" s="1">
         <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M50" s="1"/>
-    </row>
-    <row r="51" customFormat="1" ht="15" spans="1:15">
-      <c r="A51" s="5">
-        <v>69</v>
-      </c>
-      <c r="B51" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="1">
+      <c r="B51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D51" s="1"/>
-      <c r="F51" s="13">
-        <v>10013</v>
-      </c>
-      <c r="G51" s="1">
-        <v>14</v>
-      </c>
-      <c r="H51" s="1">
-        <v>80</v>
-      </c>
-      <c r="I51"/>
-      <c r="J51" s="1">
-        <v>2</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" s="2" t="s">
+      <c r="M51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:15">
+      <c r="A52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:15">
+      <c r="B52" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="15">
+        <v>400</v>
+      </c>
+      <c r="D52">
+        <v>400</v>
+      </c>
+      <c r="F52" s="1">
+        <v>11003</v>
+      </c>
+      <c r="G52" s="1">
+        <v>235</v>
+      </c>
+      <c r="H52" s="1">
+        <v>150</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+      <c r="L52" s="1"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="1"/>
+      <c r="O52">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="15" spans="1:15">
       <c r="A53" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="14" t="s">
         <v>105</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="C53" s="15">
         <v>400</v>
@@ -3427,13 +3409,13 @@
         <v>400</v>
       </c>
       <c r="F53" s="1">
-        <v>11003</v>
+        <v>11004</v>
       </c>
       <c r="G53" s="1">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="H53" s="1">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J53" s="1">
         <v>2</v>
@@ -3442,15 +3424,15 @@
       <c r="M53" s="14"/>
       <c r="N53" s="1"/>
       <c r="O53">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="15" spans="1:15">
       <c r="A54" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="15">
         <v>400</v>
@@ -3459,13 +3441,13 @@
         <v>400</v>
       </c>
       <c r="F54" s="1">
-        <v>11004</v>
+        <v>11005</v>
       </c>
       <c r="G54" s="1">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="H54" s="1">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J54" s="1">
         <v>2</v>
@@ -3474,71 +3456,78 @@
       <c r="M54" s="14"/>
       <c r="N54" s="1"/>
       <c r="O54">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" ht="15" spans="1:15">
-      <c r="A55" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A55" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="15">
-        <v>400</v>
-      </c>
-      <c r="D55">
-        <v>400</v>
-      </c>
-      <c r="F55" s="1">
-        <v>11005</v>
-      </c>
-      <c r="G55" s="1">
-        <v>133</v>
-      </c>
-      <c r="H55" s="1">
-        <v>133</v>
-      </c>
-      <c r="J55" s="1">
-        <v>2</v>
-      </c>
-      <c r="L55" s="1"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="1"/>
-      <c r="O55">
-        <v>17</v>
-      </c>
+      <c r="B55" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M55" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N55" s="13"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A56" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>111</v>
+      <c r="A56" s="13">
+        <v>70001</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>114</v>
       </c>
       <c r="D56" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>114</v>
+      <c r="F56" s="13">
+        <v>1042</v>
+      </c>
+      <c r="G56" s="13">
+        <v>123</v>
+      </c>
+      <c r="H56" s="13">
+        <v>93</v>
       </c>
       <c r="I56" s="13" t="s">
         <v>15</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L56" s="13" t="s">
         <v>15</v>
@@ -3550,34 +3539,34 @@
     </row>
     <row r="57" s="2" customFormat="1" ht="15" spans="1:15">
       <c r="A57" s="13">
-        <v>70001</v>
+        <v>70002</v>
       </c>
       <c r="B57" s="17" t="s">
         <v>115</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="13">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G57" s="13">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="H57" s="13">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>15</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="L57" s="13" t="s">
         <v>15</v>
@@ -3586,45 +3575,6 @@
         <v>15</v>
       </c>
       <c r="N57" s="13"/>
-    </row>
-    <row r="58" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A58" s="13">
-        <v>70002</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" s="13">
-        <v>1043</v>
-      </c>
-      <c r="G58" s="13">
-        <v>103</v>
-      </c>
-      <c r="H58" s="13">
-        <v>180</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N58" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15">
@@ -3636,27 +3586,24 @@
   <conditionalFormatting sqref="A33">
     <cfRule type="duplicateValues" dxfId="0" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A39">
+  <conditionalFormatting sqref="A38">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
+  <conditionalFormatting sqref="F50">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
     <cfRule type="duplicateValues" dxfId="1" priority="19"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A58">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A23">
     <cfRule type="duplicateValues" dxfId="0" priority="84"/>
@@ -3667,17 +3614,17 @@
   <conditionalFormatting sqref="A28:A30">
     <cfRule type="duplicateValues" dxfId="0" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50:A51">
+  <conditionalFormatting sqref="A49:A50">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A33 A35:A38 A40:A49 A52:A56 A59:A1048576">
+  <conditionalFormatting sqref="A1:A37 A39:A48 A51:A55 A58:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="25"/>
     <cfRule type="duplicateValues" dxfId="0" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A35:A38 A40:A49 A52:A56 A59:A1048576">
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A48 A51:A55 A58:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A35:A38 A40:A48 A52:A56 A59:A1048576">
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A47 A51:A55 A58:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="112"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="116">
   <si>
     <t>序号</t>
   </si>
@@ -179,154 +179,154 @@
     <t>linegroup</t>
   </si>
   <si>
-    <t>勇者大陆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仙踪林  </t>
-  </si>
-  <si>
-    <t>幻术园一</t>
-  </si>
-  <si>
-    <t>幻术园二</t>
-  </si>
-  <si>
-    <t>幻术园三</t>
-  </si>
-  <si>
-    <t>冰风谷一</t>
-  </si>
-  <si>
-    <t>冰风谷二</t>
-  </si>
-  <si>
-    <t>冰风谷三</t>
-  </si>
-  <si>
-    <t>冰风谷四</t>
-  </si>
-  <si>
-    <t>地下城一</t>
-  </si>
-  <si>
-    <t>地下城二</t>
-  </si>
-  <si>
-    <t>地下城三</t>
-  </si>
-  <si>
-    <t>失落之塔一</t>
-  </si>
-  <si>
-    <t>失落之塔二</t>
-  </si>
-  <si>
-    <t>失落之塔三</t>
-  </si>
-  <si>
-    <t>失落之塔四</t>
-  </si>
-  <si>
-    <t>失落之塔五</t>
-  </si>
-  <si>
-    <t>失落之塔六</t>
-  </si>
-  <si>
-    <t>失落之塔七</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯一</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯二</t>
-  </si>
-  <si>
-    <t>亚特兰蒂斯三</t>
+    <t>Lorencia</t>
+  </si>
+  <si>
+    <t>Noria</t>
+  </si>
+  <si>
+    <t>Elbeland 1</t>
+  </si>
+  <si>
+    <t>Elbeland 2</t>
+  </si>
+  <si>
+    <t>Elbeland 3</t>
+  </si>
+  <si>
+    <t>Devias 1</t>
+  </si>
+  <si>
+    <t>Devias 2</t>
+  </si>
+  <si>
+    <t>Devias 3</t>
+  </si>
+  <si>
+    <t>Devias 4</t>
+  </si>
+  <si>
+    <t>Dungeon 1</t>
+  </si>
+  <si>
+    <t>Dungeon 2</t>
+  </si>
+  <si>
+    <t>Dungeon 3</t>
+  </si>
+  <si>
+    <t>Lost Tower 1</t>
+  </si>
+  <si>
+    <t>Lost Tower 2</t>
+  </si>
+  <si>
+    <t>Lost Tower 3</t>
+  </si>
+  <si>
+    <t>Lost Tower 4</t>
+  </si>
+  <si>
+    <t>Lost Tower 5</t>
+  </si>
+  <si>
+    <t>Lost Tower 6</t>
+  </si>
+  <si>
+    <t>Lost Tower 7</t>
+  </si>
+  <si>
+    <t>Atlantis 1</t>
+  </si>
+  <si>
+    <t>Atlantis 2</t>
+  </si>
+  <si>
+    <t>Atlantis 3</t>
   </si>
   <si>
     <t>checkLevel&gt;99999</t>
   </si>
   <si>
-    <t>死亡沙漠一</t>
-  </si>
-  <si>
-    <t>死亡沙漠二</t>
-  </si>
-  <si>
-    <t>幽暗森林一</t>
-  </si>
-  <si>
-    <t>幽暗森林二</t>
-  </si>
-  <si>
-    <t>天空之城</t>
+    <t>Desert 1</t>
+  </si>
+  <si>
+    <t>Desert 2</t>
+  </si>
+  <si>
+    <t>Swamp of Calmness 1</t>
+  </si>
+  <si>
+    <t>Swamp of Calmness 2</t>
+  </si>
+  <si>
+    <t>Sky Temple</t>
   </si>
   <si>
     <t>checkWearEquip[14]&gt;0</t>
   </si>
   <si>
-    <t>坎特鲁废墟一</t>
-  </si>
-  <si>
-    <t>坎特鲁废墟二</t>
-  </si>
-  <si>
-    <t>坎特鲁遗址一</t>
-  </si>
-  <si>
-    <t>坎特鲁遗址二</t>
-  </si>
-  <si>
-    <t>冰霜之城一</t>
-  </si>
-  <si>
-    <t>冰霜之城二</t>
-  </si>
-  <si>
-    <t>冰霜之城三</t>
-  </si>
-  <si>
-    <t>安宁池</t>
-  </si>
-  <si>
-    <t>恶魔广场1</t>
-  </si>
-  <si>
-    <t>恶魔广场2</t>
-  </si>
-  <si>
-    <t>恶魔广场3</t>
-  </si>
-  <si>
-    <t>恶魔广场4</t>
-  </si>
-  <si>
-    <t>恶魔广场5</t>
-  </si>
-  <si>
-    <t>恶魔广场6</t>
-  </si>
-  <si>
-    <t>恶魔广场7</t>
-  </si>
-  <si>
-    <t>血色城堡</t>
-  </si>
-  <si>
-    <t>罗兰峡谷</t>
-  </si>
-  <si>
-    <t>狼魂要塞</t>
-  </si>
-  <si>
-    <t>战盟BOSS</t>
+    <t>Kanturu Ruins 1</t>
+  </si>
+  <si>
+    <t>Kanturu Ruins 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanturu Remain </t>
+  </si>
+  <si>
+    <t>Kanturu Remain2</t>
+  </si>
+  <si>
+    <t>Ice Castle 1</t>
+  </si>
+  <si>
+    <t>Ice Castle 2</t>
+  </si>
+  <si>
+    <t>Ice Castle 3</t>
+  </si>
+  <si>
+    <t>Aida</t>
+  </si>
+  <si>
+    <t>Devil Square 1</t>
+  </si>
+  <si>
+    <t>Devil Square 2</t>
+  </si>
+  <si>
+    <t>Devil Square 3</t>
+  </si>
+  <si>
+    <t>Devil Square 4</t>
+  </si>
+  <si>
+    <t>Devil Square 5</t>
+  </si>
+  <si>
+    <t>Devil Square 6</t>
+  </si>
+  <si>
+    <t>Devil Square 7</t>
+  </si>
+  <si>
+    <t>Blood Castle</t>
+  </si>
+  <si>
+    <t>Castle Siege Valley</t>
+  </si>
+  <si>
+    <t>Wolf Fortress</t>
+  </si>
+  <si>
+    <t>Guild Boss</t>
   </si>
   <si>
     <t>57</t>
   </si>
   <si>
-    <t>赤色要塞</t>
+    <t>Chaos Castle</t>
   </si>
   <si>
     <t>1</t>
@@ -347,25 +347,25 @@
     <t>73</t>
   </si>
   <si>
-    <t>菲利亚</t>
+    <t>Ferea</t>
   </si>
   <si>
     <t>74</t>
   </si>
   <si>
-    <t>尼克西斯湖</t>
+    <t>Lake Nixis</t>
   </si>
   <si>
     <t>75</t>
   </si>
   <si>
-    <t>深渊地下城</t>
+    <t>Abyss Dungeon</t>
   </si>
   <si>
     <t>12005</t>
   </si>
   <si>
-    <t>卡利玛神庙</t>
+    <t>Kalima</t>
   </si>
   <si>
     <t>1025</t>
@@ -377,10 +377,10 @@
     <t>22</t>
   </si>
   <si>
-    <t>巴卡斯兵营</t>
-  </si>
-  <si>
-    <t>巴卡斯休息室</t>
+    <t>Barkas Barracks</t>
+  </si>
+  <si>
+    <t>Barkas Rest Area</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1044,29 +1044,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1688,7 +1670,7 @@
       <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="1">
@@ -1725,7 +1707,7 @@
       <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>49</v>
       </c>
       <c r="C6" s="1">
@@ -1752,10 +1734,10 @@
       <c r="K6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
       <c r="N6" s="1"/>
-      <c r="O6" s="3">
+      <c r="O6" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1763,7 +1745,7 @@
       <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>50</v>
       </c>
       <c r="C7" s="1">
@@ -1786,9 +1768,9 @@
         <v>2</v>
       </c>
       <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="O7" s="3">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="O7" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1817,7 +1799,9 @@
       <c r="J8" s="1">
         <v>2</v>
       </c>
-      <c r="O8" s="3">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="O8" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1846,7 +1830,9 @@
       <c r="J9" s="1">
         <v>2</v>
       </c>
-      <c r="O9" s="3">
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="O9" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1854,14 +1840,14 @@
       <c r="A10" s="5">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
@@ -1881,9 +1867,9 @@
       <c r="K10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="O10" s="3">
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="O10" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1895,10 +1881,10 @@
         <v>54</v>
       </c>
       <c r="C11" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1">
         <v>1003</v>
@@ -1912,7 +1898,9 @@
       <c r="J11" s="1">
         <v>2</v>
       </c>
-      <c r="O11" s="3">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="O11" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1924,10 +1912,10 @@
         <v>55</v>
       </c>
       <c r="C12" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1">
         <v>1003</v>
@@ -1941,7 +1929,9 @@
       <c r="J12" s="1">
         <v>2</v>
       </c>
-      <c r="O12" s="3">
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="O12" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1953,10 +1943,10 @@
         <v>56</v>
       </c>
       <c r="C13" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1">
         <v>1003</v>
@@ -1970,7 +1960,9 @@
       <c r="J13" s="1">
         <v>2</v>
       </c>
-      <c r="O13" s="3">
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="O13" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1982,10 +1974,10 @@
         <v>57</v>
       </c>
       <c r="C14" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D14" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>15</v>
@@ -2006,9 +1998,9 @@
       <c r="K14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="O14" s="3">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="O14" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2020,10 +2012,10 @@
         <v>58</v>
       </c>
       <c r="C15" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>15</v>
@@ -2044,9 +2036,9 @@
       <c r="K15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="O15" s="3">
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="O15" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2082,9 +2074,9 @@
       <c r="K16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="O16" s="3">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="O16" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2096,10 +2088,10 @@
         <v>60</v>
       </c>
       <c r="C17" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D17" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>15</v>
@@ -2120,9 +2112,9 @@
       <c r="K17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="O17" s="3">
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="O17" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2134,10 +2126,10 @@
         <v>61</v>
       </c>
       <c r="C18" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D18" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>15</v>
@@ -2158,9 +2150,9 @@
       <c r="K18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="O18" s="3">
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="O18" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2172,10 +2164,10 @@
         <v>62</v>
       </c>
       <c r="C19" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D19" s="1">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>15</v>
@@ -2196,9 +2188,9 @@
       <c r="K19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="O19" s="3">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="O19" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2234,9 +2226,9 @@
       <c r="K20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="O20" s="3">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="O20" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2272,9 +2264,9 @@
       <c r="K21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="O21" s="3">
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="O21" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2310,9 +2302,9 @@
       <c r="K22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="O22" s="3">
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="O22" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2348,9 +2340,9 @@
       <c r="K23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="O23" s="3">
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="O23" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2362,10 +2354,10 @@
         <v>67</v>
       </c>
       <c r="C24" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>15</v>
@@ -2386,10 +2378,10 @@
       <c r="K24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
       <c r="N24" s="1"/>
-      <c r="O24" s="3">
+      <c r="O24" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2401,10 +2393,10 @@
         <v>68</v>
       </c>
       <c r="C25" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D25" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>15</v>
@@ -2425,10 +2417,10 @@
       <c r="K25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
       <c r="N25" s="1"/>
-      <c r="O25" s="3">
+      <c r="O25" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2440,10 +2432,10 @@
         <v>69</v>
       </c>
       <c r="C26" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D26" s="1">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>15</v>
@@ -2464,10 +2456,10 @@
       <c r="K26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
       <c r="N26" s="1"/>
-      <c r="O26" s="3">
+      <c r="O26" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2479,10 +2471,10 @@
         <v>71</v>
       </c>
       <c r="C27" s="9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D27" s="9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>15</v>
@@ -2503,10 +2495,10 @@
       <c r="K27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="3">
+      <c r="O27" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2518,10 +2510,10 @@
         <v>72</v>
       </c>
       <c r="C28" s="9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D28" s="9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>15</v>
@@ -2542,10 +2534,10 @@
       <c r="K28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
       <c r="N28" s="1"/>
-      <c r="O28" s="3">
+      <c r="O28" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2557,10 +2549,10 @@
         <v>73</v>
       </c>
       <c r="C29" s="1">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D29" s="1">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F29" s="5">
         <v>1034</v>
@@ -2574,7 +2566,9 @@
       <c r="J29" s="1">
         <v>2</v>
       </c>
-      <c r="O29" s="3">
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="O29" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2586,10 +2580,10 @@
         <v>74</v>
       </c>
       <c r="C30" s="1">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F30" s="5">
         <v>1034</v>
@@ -2603,7 +2597,9 @@
       <c r="J30" s="1">
         <v>2</v>
       </c>
-      <c r="O30" s="3">
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="O30" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2615,10 +2611,10 @@
         <v>75</v>
       </c>
       <c r="C31" s="9">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="D31" s="9">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="E31" t="s">
         <v>76</v>
@@ -2637,10 +2633,10 @@
         <v>2</v>
       </c>
       <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="3">
+      <c r="O31" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2652,10 +2648,10 @@
         <v>77</v>
       </c>
       <c r="C32" s="9">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="D32" s="9">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="F32" s="1">
         <v>1038</v>
@@ -2673,10 +2669,10 @@
       <c r="K32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
       <c r="N32" s="1"/>
-      <c r="O32" s="3">
+      <c r="O32" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2688,10 +2684,10 @@
         <v>78</v>
       </c>
       <c r="C33" s="9">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D33" s="9">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="F33" s="1">
         <v>1038</v>
@@ -2709,10 +2705,10 @@
       <c r="K33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
       <c r="N33" s="1"/>
-      <c r="O33" s="3">
+      <c r="O33" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2724,10 +2720,10 @@
         <v>79</v>
       </c>
       <c r="C34" s="9">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="D34" s="9">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>15</v>
@@ -2748,10 +2744,10 @@
       <c r="K34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
       <c r="N34" s="1"/>
-      <c r="O34" s="3">
+      <c r="O34" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2763,10 +2759,10 @@
         <v>80</v>
       </c>
       <c r="C35" s="9">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="D35" s="9">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>15</v>
@@ -2786,7 +2782,9 @@
       <c r="K35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O35" s="3">
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="O35" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2798,10 +2796,10 @@
         <v>81</v>
       </c>
       <c r="C36" s="9">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="D36" s="9">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>15</v>
@@ -2822,25 +2820,25 @@
       <c r="K36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="15" spans="1:15">
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:15">
       <c r="A37" s="1">
         <v>2801</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="1">
-        <v>300</v>
-      </c>
-      <c r="D37" s="1">
-        <v>300</v>
+      <c r="C37" s="9">
+        <v>330</v>
+      </c>
+      <c r="D37" s="9">
+        <v>330</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>15</v>
@@ -2860,23 +2858,24 @@
       <c r="K37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M37" s="10"/>
-      <c r="O37" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="15" spans="1:15">
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="O37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:15">
       <c r="A38" s="1">
         <v>2802</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="1">
-        <v>320</v>
-      </c>
-      <c r="D38" s="1">
-        <v>320</v>
+      <c r="C38" s="9">
+        <v>330</v>
+      </c>
+      <c r="D38" s="9">
+        <v>330</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>15</v>
@@ -2896,16 +2895,17 @@
       <c r="K38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M38" s="10"/>
-      <c r="O38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="15" spans="1:15">
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="O38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:15">
       <c r="A39" s="5">
         <v>31</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="8" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="1">
@@ -2929,10 +2929,10 @@
       <c r="K39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L39" s="1"/>
-      <c r="M39" s="11"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="3">
+      <c r="O39" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       <c r="A40" s="5">
         <v>48</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="5">
@@ -2964,19 +2964,15 @@
       <c r="K40" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
       <c r="O40" s="3"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="5">
         <v>49</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>86</v>
       </c>
       <c r="D41" s="5">
@@ -3000,12 +2996,8 @@
       <c r="K41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
       <c r="O41" s="3"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
@@ -3036,12 +3028,8 @@
       <c r="K42" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
       <c r="O42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
@@ -3072,12 +3060,8 @@
       <c r="K43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
       <c r="O43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
@@ -3108,12 +3092,8 @@
       <c r="K44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
       <c r="O44" s="3"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
@@ -3144,12 +3124,8 @@
       <c r="K45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
       <c r="O45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
@@ -3180,12 +3156,8 @@
       <c r="K46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
       <c r="O46" s="3"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:15">
@@ -3216,19 +3188,15 @@
       <c r="K47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
       <c r="O47" s="3"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:15">
       <c r="A48" s="1">
         <v>16001</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>93</v>
       </c>
       <c r="D48" s="5">
@@ -3252,19 +3220,15 @@
       <c r="K48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
       <c r="O48" s="3"/>
     </row>
     <row r="49" customFormat="1" spans="1:15">
       <c r="A49" s="5">
         <v>33</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" t="s">
         <v>94</v>
       </c>
       <c r="C49" s="5">
@@ -3289,23 +3253,19 @@
       <c r="K49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M49" s="1"/>
     </row>
     <row r="50" customFormat="1" ht="15" spans="1:15">
       <c r="A50" s="5">
         <v>69</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" t="s">
         <v>95</v>
       </c>
       <c r="C50" s="1">
         <v>70</v>
       </c>
       <c r="D50" s="1"/>
-      <c r="F50" s="13">
+      <c r="F50" s="10">
         <v>10013</v>
       </c>
       <c r="G50" s="1">
@@ -3326,7 +3286,7 @@
       <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -3355,9 +3315,6 @@
       </c>
       <c r="K51" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>15</v>
@@ -3367,10 +3324,10 @@
       <c r="A52" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="11">
         <v>400</v>
       </c>
       <c r="D52">
@@ -3388,25 +3345,23 @@
       <c r="J52" s="1">
         <v>2</v>
       </c>
-      <c r="L52" s="1"/>
-      <c r="M52" s="14"/>
       <c r="N52" s="1"/>
-      <c r="O52">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" ht="15" spans="1:15">
+      <c r="O52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:15">
       <c r="A53" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="15">
-        <v>400</v>
+      <c r="C53" s="11">
+        <v>500</v>
       </c>
       <c r="D53">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F53" s="1">
         <v>11004</v>
@@ -3420,25 +3375,23 @@
       <c r="J53" s="1">
         <v>2</v>
       </c>
-      <c r="L53" s="1"/>
-      <c r="M53" s="14"/>
       <c r="N53" s="1"/>
-      <c r="O53">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" ht="15" spans="1:15">
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:15">
       <c r="A54" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="15">
-        <v>400</v>
+      <c r="C54" s="11">
+        <v>300</v>
       </c>
       <c r="D54">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F54" s="1">
         <v>11005</v>
@@ -3452,129 +3405,127 @@
       <c r="J54" s="1">
         <v>2</v>
       </c>
-      <c r="L54" s="1"/>
-      <c r="M54" s="14"/>
       <c r="N54" s="1"/>
-      <c r="O54">
-        <v>17</v>
+      <c r="O54" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="55" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="13" t="s">
+      <c r="E55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="G55" s="13" t="s">
+      <c r="G55" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H55" s="13" t="s">
+      <c r="H55" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I55" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" s="13" t="s">
+      <c r="I55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K55" s="13" t="s">
+      <c r="K55" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L55" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M55" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N55" s="13"/>
+      <c r="L55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N55" s="10"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A56" s="13">
+      <c r="A56" s="10">
         <v>70001</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" s="13">
+      <c r="E56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="10">
         <v>1042</v>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="10">
         <v>123</v>
       </c>
-      <c r="H56" s="13">
+      <c r="H56" s="10">
         <v>93</v>
       </c>
-      <c r="I56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" s="13" t="s">
+      <c r="I56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K56" s="13" t="s">
+      <c r="K56" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N56" s="13"/>
+      <c r="L56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N56" s="10"/>
     </row>
     <row r="57" s="2" customFormat="1" ht="15" spans="1:15">
-      <c r="A57" s="13">
+      <c r="A57" s="10">
         <v>70002</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" t="s">
         <v>115</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="13">
+      <c r="E57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="10">
         <v>1043</v>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="10">
         <v>103</v>
       </c>
-      <c r="H57" s="13">
+      <c r="H57" s="10">
         <v>180</v>
       </c>
-      <c r="I57" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" s="13" t="s">
+      <c r="I57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K57" s="13" t="s">
+      <c r="K57" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L57" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="M57" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="N57" s="13"/>
+      <c r="L57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N57" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_mapMove.xlsx
@@ -3,11 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$B$1:$B$48</definedName>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="169">
   <si>
     <t>序号</t>
   </si>
@@ -179,6 +185,210 @@
     <t>linegroup</t>
   </si>
   <si>
+    <t>勇者大陆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仙踪林  </t>
+  </si>
+  <si>
+    <t>幻术园一</t>
+  </si>
+  <si>
+    <t>幻术园二</t>
+  </si>
+  <si>
+    <t>幻术园三</t>
+  </si>
+  <si>
+    <t>冰风谷一</t>
+  </si>
+  <si>
+    <t>冰风谷二</t>
+  </si>
+  <si>
+    <t>冰风谷三</t>
+  </si>
+  <si>
+    <t>冰风谷四</t>
+  </si>
+  <si>
+    <t>地下城一</t>
+  </si>
+  <si>
+    <t>地下城二</t>
+  </si>
+  <si>
+    <t>地下城三</t>
+  </si>
+  <si>
+    <t>失落之塔一</t>
+  </si>
+  <si>
+    <t>失落之塔二</t>
+  </si>
+  <si>
+    <t>失落之塔三</t>
+  </si>
+  <si>
+    <t>失落之塔四</t>
+  </si>
+  <si>
+    <t>失落之塔五</t>
+  </si>
+  <si>
+    <t>失落之塔六</t>
+  </si>
+  <si>
+    <t>失落之塔七</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯一</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯二</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯三</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;99999</t>
+  </si>
+  <si>
+    <t>死亡沙漠一</t>
+  </si>
+  <si>
+    <t>死亡沙漠二</t>
+  </si>
+  <si>
+    <t>幽暗森林一</t>
+  </si>
+  <si>
+    <t>幽暗森林二</t>
+  </si>
+  <si>
+    <t>天空之城</t>
+  </si>
+  <si>
+    <t>checkWearEquip[14]&gt;0</t>
+  </si>
+  <si>
+    <t>坎特鲁废墟一</t>
+  </si>
+  <si>
+    <t>坎特鲁废墟二</t>
+  </si>
+  <si>
+    <t>坎特鲁遗址一</t>
+  </si>
+  <si>
+    <t>坎特鲁遗址二</t>
+  </si>
+  <si>
+    <t>冰霜之城一</t>
+  </si>
+  <si>
+    <t>冰霜之城二</t>
+  </si>
+  <si>
+    <t>冰霜之城三</t>
+  </si>
+  <si>
+    <t>安宁池</t>
+  </si>
+  <si>
+    <t>恶魔广场1</t>
+  </si>
+  <si>
+    <t>恶魔广场2</t>
+  </si>
+  <si>
+    <t>恶魔广场3</t>
+  </si>
+  <si>
+    <t>恶魔广场4</t>
+  </si>
+  <si>
+    <t>恶魔广场5</t>
+  </si>
+  <si>
+    <t>恶魔广场6</t>
+  </si>
+  <si>
+    <t>恶魔广场7</t>
+  </si>
+  <si>
+    <t>血色城堡</t>
+  </si>
+  <si>
+    <t>罗兰峡谷</t>
+  </si>
+  <si>
+    <t>狼魂要塞</t>
+  </si>
+  <si>
+    <t>战盟BOSS</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>赤色要塞</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>菲利亚</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>尼克西斯湖</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>深渊地下城</t>
+  </si>
+  <si>
+    <t>12005</t>
+  </si>
+  <si>
+    <t>卡利玛神庙</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>巴卡斯兵营</t>
+  </si>
+  <si>
+    <t>巴卡斯休息室</t>
+  </si>
+  <si>
     <t>Lorencia</t>
   </si>
   <si>
@@ -245,9 +455,6 @@
     <t>Atlantis 3</t>
   </si>
   <si>
-    <t>checkLevel&gt;99999</t>
-  </si>
-  <si>
     <t>Desert 1</t>
   </si>
   <si>
@@ -263,9 +470,6 @@
     <t>Sky Temple</t>
   </si>
   <si>
-    <t>checkWearEquip[14]&gt;0</t>
-  </si>
-  <si>
     <t>Kanturu Ruins 1</t>
   </si>
   <si>
@@ -323,58 +527,19 @@
     <t>Guild Boss</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>Chaos Castle</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1019</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
     <t>Ferea</t>
   </si>
   <si>
-    <t>74</t>
-  </si>
-  <si>
     <t>Lake Nixis</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>Abyss Dungeon</t>
   </si>
   <si>
-    <t>12005</t>
-  </si>
-  <si>
     <t>Kalima</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>22</t>
   </si>
   <si>
     <t>Barkas Barracks</t>
@@ -1017,7 +1182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1049,6 +1214,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1460,6 +1640,2156 @@
   <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="17.0166666666667" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="30.575" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="1"/>
+    <col min="7" max="7" width="34.6333333333333" customWidth="1"/>
+    <col min="8" max="8" width="37.6333333333333" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
+    <col min="10" max="10" width="9.375"/>
+    <col min="11" max="11" width="46.625" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="21.625" customWidth="1"/>
+    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="17.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="54" spans="1:15">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:15">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="G5" s="1">
+        <v>134</v>
+      </c>
+      <c r="H5" s="1">
+        <v>128</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1004</v>
+      </c>
+      <c r="G6" s="5">
+        <v>176</v>
+      </c>
+      <c r="H6" s="5">
+        <v>116</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:15">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1052</v>
+      </c>
+      <c r="G7" s="5">
+        <v>51</v>
+      </c>
+      <c r="H7" s="5">
+        <v>224</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:15">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1052</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>57</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:15">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1052</v>
+      </c>
+      <c r="G9" s="1">
+        <v>194</v>
+      </c>
+      <c r="H9" s="1">
+        <v>144</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:15">
+      <c r="A10" s="5">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1003</v>
+      </c>
+      <c r="G10" s="1">
+        <v>202</v>
+      </c>
+      <c r="H10" s="1">
+        <v>44</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:15">
+      <c r="A11" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1003</v>
+      </c>
+      <c r="G11" s="1">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>25</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:15">
+      <c r="A12" s="1">
+        <v>4002</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1003</v>
+      </c>
+      <c r="G12" s="1">
+        <v>224</v>
+      </c>
+      <c r="H12" s="1">
+        <v>216</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:15">
+      <c r="A13" s="1">
+        <v>4003</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1003</v>
+      </c>
+      <c r="G13" s="1">
+        <v>69</v>
+      </c>
+      <c r="H13" s="1">
+        <v>178</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:15">
+      <c r="A14" s="5">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="1">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1002</v>
+      </c>
+      <c r="G14" s="7">
+        <v>108</v>
+      </c>
+      <c r="H14" s="7">
+        <v>239</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:15">
+      <c r="A15" s="1">
+        <v>5001</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="1">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1102</v>
+      </c>
+      <c r="G15" s="7">
+        <v>229</v>
+      </c>
+      <c r="H15" s="7">
+        <v>123</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
+      <c r="A16" s="1">
+        <v>5002</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1">
+        <v>50</v>
+      </c>
+      <c r="D16" s="1">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1202</v>
+      </c>
+      <c r="G16" s="7">
+        <v>6</v>
+      </c>
+      <c r="H16" s="7">
+        <v>85</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="O16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:15">
+      <c r="A17" s="5">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1005</v>
+      </c>
+      <c r="G17" s="1">
+        <v>208</v>
+      </c>
+      <c r="H17" s="1">
+        <v>77</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="O17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:15">
+      <c r="A18" s="1">
+        <v>8001</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1">
+        <v>50</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1105</v>
+      </c>
+      <c r="G18" s="1">
+        <v>242</v>
+      </c>
+      <c r="H18" s="1">
+        <v>237</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="O18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:15">
+      <c r="A19" s="1">
+        <v>8002</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="1">
+        <v>50</v>
+      </c>
+      <c r="D19" s="1">
+        <v>50</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1205</v>
+      </c>
+      <c r="G19" s="1">
+        <v>87</v>
+      </c>
+      <c r="H19" s="1">
+        <v>169</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:15">
+      <c r="A20" s="1">
+        <v>8003</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1">
+        <v>80</v>
+      </c>
+      <c r="D20" s="1">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1305</v>
+      </c>
+      <c r="G20" s="1">
+        <v>85</v>
+      </c>
+      <c r="H20" s="1">
+        <v>91</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="O20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:15">
+      <c r="A21" s="1">
+        <v>8004</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="1">
+        <v>80</v>
+      </c>
+      <c r="D21" s="1">
+        <v>80</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1405</v>
+      </c>
+      <c r="G21" s="1">
+        <v>130</v>
+      </c>
+      <c r="H21" s="1">
+        <v>54</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:15">
+      <c r="A22" s="1">
+        <v>8005</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="1">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1">
+        <v>80</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1505</v>
+      </c>
+      <c r="G22" s="1">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1">
+        <v>55</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:15">
+      <c r="A23" s="1">
+        <v>8006</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="1">
+        <v>80</v>
+      </c>
+      <c r="D23" s="1">
+        <v>80</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1605</v>
+      </c>
+      <c r="G23" s="1">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1">
+        <v>86</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="O23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:15">
+      <c r="A24" s="1">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="1">
+        <v>70</v>
+      </c>
+      <c r="D24" s="1">
+        <v>70</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1008</v>
+      </c>
+      <c r="G24" s="1">
+        <v>23</v>
+      </c>
+      <c r="H24" s="1">
+        <v>19</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:15">
+      <c r="A25" s="1">
+        <v>15001</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="1">
+        <v>70</v>
+      </c>
+      <c r="D25" s="1">
+        <v>70</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1008</v>
+      </c>
+      <c r="G25" s="1">
+        <v>228</v>
+      </c>
+      <c r="H25" s="1">
+        <v>46</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:15">
+      <c r="A26" s="1">
+        <v>15002</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="1">
+        <v>70</v>
+      </c>
+      <c r="D26" s="1">
+        <v>70</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1008</v>
+      </c>
+      <c r="G26" s="1">
+        <v>58</v>
+      </c>
+      <c r="H26" s="1">
+        <v>176</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:15">
+      <c r="A27" s="5">
+        <v>17</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="9">
+        <v>140</v>
+      </c>
+      <c r="D27" s="9">
+        <v>140</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1009</v>
+      </c>
+      <c r="G27" s="1">
+        <v>190</v>
+      </c>
+      <c r="H27" s="1">
+        <v>58</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:15">
+      <c r="A28" s="1">
+        <v>17001</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="9">
+        <v>140</v>
+      </c>
+      <c r="D28" s="9">
+        <v>140</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="5">
+        <v>1009</v>
+      </c>
+      <c r="G28" s="1">
+        <v>104</v>
+      </c>
+      <c r="H28" s="1">
+        <v>144</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:15">
+      <c r="A29" s="5">
+        <v>19</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1">
+        <v>170</v>
+      </c>
+      <c r="D29" s="1">
+        <v>170</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1034</v>
+      </c>
+      <c r="G29" s="1">
+        <v>87</v>
+      </c>
+      <c r="H29" s="1">
+        <v>11</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2</v>
+      </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:15">
+      <c r="A30" s="5">
+        <v>20</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1">
+        <v>170</v>
+      </c>
+      <c r="D30" s="1">
+        <v>170</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1034</v>
+      </c>
+      <c r="G30" s="7">
+        <v>117</v>
+      </c>
+      <c r="H30" s="7">
+        <v>103</v>
+      </c>
+      <c r="J30" s="1">
+        <v>2</v>
+      </c>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="O30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:15">
+      <c r="A31" s="5">
+        <v>21</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="9">
+        <v>160</v>
+      </c>
+      <c r="D31" s="9">
+        <v>160</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1011</v>
+      </c>
+      <c r="G31" s="1">
+        <v>16</v>
+      </c>
+      <c r="H31" s="1">
+        <v>20</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:15">
+      <c r="A32" s="5">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="9">
+        <v>170</v>
+      </c>
+      <c r="D32" s="9">
+        <v>170</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1038</v>
+      </c>
+      <c r="G32" s="1">
+        <v>24</v>
+      </c>
+      <c r="H32" s="1">
+        <v>215</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:15">
+      <c r="A33" s="1">
+        <v>24001</v>
+      </c>
+      <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="9">
+        <v>230</v>
+      </c>
+      <c r="D33" s="9">
+        <v>230</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1038</v>
+      </c>
+      <c r="G33" s="1">
+        <v>203</v>
+      </c>
+      <c r="H33" s="1">
+        <v>38</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1">
+        <v>2</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:15">
+      <c r="A34" s="5">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="9">
+        <v>230</v>
+      </c>
+      <c r="D34" s="9">
+        <v>230</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1039</v>
+      </c>
+      <c r="G34" s="1">
+        <v>80</v>
+      </c>
+      <c r="H34" s="1">
+        <v>105</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:15">
+      <c r="A35" s="1">
+        <v>2601</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="9">
+        <v>230</v>
+      </c>
+      <c r="D35" s="9">
+        <v>230</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1039</v>
+      </c>
+      <c r="G35" s="1">
+        <v>108</v>
+      </c>
+      <c r="H35" s="1">
+        <v>139</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="O35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:15">
+      <c r="A36" s="5">
+        <v>28</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="9">
+        <v>280</v>
+      </c>
+      <c r="D36" s="9">
+        <v>280</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1058</v>
+      </c>
+      <c r="G36" s="1">
+        <v>216</v>
+      </c>
+      <c r="H36" s="1">
+        <v>205</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1">
+        <v>2</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:15">
+      <c r="A37" s="1">
+        <v>2801</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="1">
+        <v>300</v>
+      </c>
+      <c r="D37" s="1">
+        <v>300</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1058</v>
+      </c>
+      <c r="G37" s="7">
+        <v>101</v>
+      </c>
+      <c r="H37" s="7">
+        <v>209</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="O37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:15">
+      <c r="A38" s="1">
+        <v>2802</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="1">
+        <v>320</v>
+      </c>
+      <c r="D38" s="1">
+        <v>320</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1058</v>
+      </c>
+      <c r="G38" s="7">
+        <v>194</v>
+      </c>
+      <c r="H38" s="7">
+        <v>24</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="O38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="15" spans="1:15">
+      <c r="A39" s="5">
+        <v>31</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="1">
+        <v>350</v>
+      </c>
+      <c r="D39" s="1">
+        <v>350</v>
+      </c>
+      <c r="F39" s="5">
+        <v>1057</v>
+      </c>
+      <c r="G39" s="1">
+        <v>140</v>
+      </c>
+      <c r="H39" s="1">
+        <v>108</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:15">
+      <c r="A40" s="5">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G40" s="1">
+        <v>136</v>
+      </c>
+      <c r="H40" s="1">
+        <v>97</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:15">
+      <c r="A41" s="5">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G41" s="1">
+        <v>126</v>
+      </c>
+      <c r="H41" s="1">
+        <v>87</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:15">
+      <c r="A42" s="5">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G42" s="1">
+        <v>143</v>
+      </c>
+      <c r="H42" s="1">
+        <v>108</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:15">
+      <c r="A43" s="5">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G43" s="1">
+        <v>142</v>
+      </c>
+      <c r="H43" s="1">
+        <v>89</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:15">
+      <c r="A44" s="5">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G44" s="5">
+        <v>133</v>
+      </c>
+      <c r="H44" s="5">
+        <v>91</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:15">
+      <c r="A45" s="5">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G45" s="5">
+        <v>135</v>
+      </c>
+      <c r="H45" s="5">
+        <v>162</v>
+      </c>
+      <c r="J45" s="1">
+        <v>2</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:15">
+      <c r="A46" s="5">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="5">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1010</v>
+      </c>
+      <c r="G46" s="5">
+        <v>135</v>
+      </c>
+      <c r="H46" s="5">
+        <v>162</v>
+      </c>
+      <c r="J46" s="1">
+        <v>2</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:15">
+      <c r="A47" s="5">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="5">
+        <v>1012</v>
+      </c>
+      <c r="G47" s="5">
+        <v>12</v>
+      </c>
+      <c r="H47" s="5">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:15">
+      <c r="A48" s="1">
+        <v>16001</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="1">
+        <v>16001</v>
+      </c>
+      <c r="G48" s="5">
+        <v>87</v>
+      </c>
+      <c r="H48" s="5">
+        <v>209</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" customFormat="1" spans="1:15">
+      <c r="A49" s="5">
+        <v>33</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="5">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49" s="5">
+        <v>1035</v>
+      </c>
+      <c r="G49" s="1">
+        <v>139</v>
+      </c>
+      <c r="H49" s="5">
+        <v>37</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="15" spans="1:15">
+      <c r="A50" s="5">
+        <v>69</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="1">
+        <v>70</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50"/>
+      <c r="F50" s="10">
+        <v>10013</v>
+      </c>
+      <c r="G50" s="1">
+        <v>14</v>
+      </c>
+      <c r="H50" s="1">
+        <v>80</v>
+      </c>
+      <c r="I50"/>
+      <c r="J50" s="1">
+        <v>2</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:15">
+      <c r="A52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C52" s="11">
+        <v>400</v>
+      </c>
+      <c r="D52">
+        <v>400</v>
+      </c>
+      <c r="E52"/>
+      <c r="F52" s="1">
+        <v>11003</v>
+      </c>
+      <c r="G52" s="1">
+        <v>235</v>
+      </c>
+      <c r="H52" s="1">
+        <v>150</v>
+      </c>
+      <c r="I52"/>
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="15" spans="1:15">
+      <c r="A53" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="11">
+        <v>400</v>
+      </c>
+      <c r="D53">
+        <v>400</v>
+      </c>
+      <c r="E53"/>
+      <c r="F53" s="1">
+        <v>11004</v>
+      </c>
+      <c r="G53" s="1">
+        <v>24</v>
+      </c>
+      <c r="H53" s="1">
+        <v>120</v>
+      </c>
+      <c r="I53"/>
+      <c r="J53" s="1">
+        <v>2</v>
+      </c>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="15" spans="1:15">
+      <c r="A54" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="11">
+        <v>400</v>
+      </c>
+      <c r="D54">
+        <v>400</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54" s="1">
+        <v>11005</v>
+      </c>
+      <c r="G54" s="1">
+        <v>133</v>
+      </c>
+      <c r="H54" s="1">
+        <v>133</v>
+      </c>
+      <c r="I54"/>
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A55" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N55" s="10"/>
+    </row>
+    <row r="56" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A56" s="10">
+        <v>70001</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1042</v>
+      </c>
+      <c r="G56" s="10">
+        <v>123</v>
+      </c>
+      <c r="H56" s="10">
+        <v>93</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N56" s="10"/>
+    </row>
+    <row r="57" s="2" customFormat="1" ht="15" spans="1:15">
+      <c r="A57" s="10">
+        <v>70002</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="10">
+        <v>1043</v>
+      </c>
+      <c r="G57" s="10">
+        <v>103</v>
+      </c>
+      <c r="H57" s="10">
+        <v>180</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N57" s="10"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A23">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28:A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49:A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A37 A39:A48 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A48 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A47 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="16.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.0166666666667" style="1" customWidth="1"/>
@@ -1671,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1697,8 +4027,6 @@
       <c r="K5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
       <c r="O5" s="1">
         <v>1</v>
       </c>
@@ -1708,7 +4036,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
@@ -1736,7 +4064,6 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="1"/>
       <c r="O6" s="1">
         <v>1</v>
       </c>
@@ -1746,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -1767,7 +4094,6 @@
       <c r="J7" s="1">
         <v>2</v>
       </c>
-      <c r="K7" s="1"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="O7" s="1">
@@ -1779,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
@@ -1810,7 +4136,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
@@ -1841,7 +4167,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="C10" s="1">
         <v>30</v>
@@ -1878,7 +4204,7 @@
         <v>4001</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1">
         <v>30</v>
@@ -1909,7 +4235,7 @@
         <v>4002</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="C12" s="1">
         <v>30</v>
@@ -1940,7 +4266,7 @@
         <v>4003</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="C13" s="1">
         <v>30</v>
@@ -1971,7 +4297,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="C14" s="1">
         <v>50</v>
@@ -1991,7 +4317,6 @@
       <c r="H14" s="7">
         <v>239</v>
       </c>
-      <c r="I14" s="1"/>
       <c r="J14" s="1">
         <v>2</v>
       </c>
@@ -2009,7 +4334,7 @@
         <v>5001</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="C15" s="1">
         <v>50</v>
@@ -2029,7 +4354,6 @@
       <c r="H15" s="7">
         <v>123</v>
       </c>
-      <c r="I15" s="1"/>
       <c r="J15" s="1">
         <v>2</v>
       </c>
@@ -2047,7 +4371,7 @@
         <v>5002</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C16" s="1">
         <v>50</v>
@@ -2067,7 +4391,6 @@
       <c r="H16" s="7">
         <v>85</v>
       </c>
-      <c r="I16" s="1"/>
       <c r="J16" s="1">
         <v>2</v>
       </c>
@@ -2085,7 +4408,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="C17" s="1">
         <v>80</v>
@@ -2105,7 +4428,6 @@
       <c r="H17" s="1">
         <v>77</v>
       </c>
-      <c r="I17" s="1"/>
       <c r="J17" s="1">
         <v>2</v>
       </c>
@@ -2123,7 +4445,7 @@
         <v>8001</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="C18" s="1">
         <v>80</v>
@@ -2143,7 +4465,6 @@
       <c r="H18" s="1">
         <v>237</v>
       </c>
-      <c r="I18" s="1"/>
       <c r="J18" s="1">
         <v>2</v>
       </c>
@@ -2161,7 +4482,7 @@
         <v>8002</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="C19" s="1">
         <v>80</v>
@@ -2181,7 +4502,6 @@
       <c r="H19" s="1">
         <v>169</v>
       </c>
-      <c r="I19" s="1"/>
       <c r="J19" s="1">
         <v>2</v>
       </c>
@@ -2199,7 +4519,7 @@
         <v>8003</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="C20" s="1">
         <v>80</v>
@@ -2219,7 +4539,6 @@
       <c r="H20" s="1">
         <v>91</v>
       </c>
-      <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>2</v>
       </c>
@@ -2237,7 +4556,7 @@
         <v>8004</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="C21" s="1">
         <v>80</v>
@@ -2257,7 +4576,6 @@
       <c r="H21" s="1">
         <v>54</v>
       </c>
-      <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2</v>
       </c>
@@ -2275,7 +4593,7 @@
         <v>8005</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C22" s="1">
         <v>80</v>
@@ -2295,7 +4613,6 @@
       <c r="H22" s="1">
         <v>55</v>
       </c>
-      <c r="I22" s="1"/>
       <c r="J22" s="1">
         <v>2</v>
       </c>
@@ -2313,7 +4630,7 @@
         <v>8006</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="C23" s="1">
         <v>80</v>
@@ -2333,7 +4650,6 @@
       <c r="H23" s="1">
         <v>86</v>
       </c>
-      <c r="I23" s="1"/>
       <c r="J23" s="1">
         <v>2</v>
       </c>
@@ -2351,7 +4667,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="C24" s="1">
         <v>100</v>
@@ -2371,7 +4687,6 @@
       <c r="H24" s="1">
         <v>19</v>
       </c>
-      <c r="I24" s="1"/>
       <c r="J24" s="1">
         <v>2</v>
       </c>
@@ -2380,7 +4695,6 @@
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
-      <c r="N24" s="1"/>
       <c r="O24" s="1">
         <v>1</v>
       </c>
@@ -2390,7 +4704,7 @@
         <v>15001</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C25" s="1">
         <v>100</v>
@@ -2410,7 +4724,6 @@
       <c r="H25" s="1">
         <v>46</v>
       </c>
-      <c r="I25" s="1"/>
       <c r="J25" s="1">
         <v>2</v>
       </c>
@@ -2419,7 +4732,6 @@
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="1"/>
       <c r="O25" s="1">
         <v>1</v>
       </c>
@@ -2429,7 +4741,7 @@
         <v>15002</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -2449,7 +4761,6 @@
       <c r="H26" s="1">
         <v>176</v>
       </c>
-      <c r="I26" s="1"/>
       <c r="J26" s="1">
         <v>2</v>
       </c>
@@ -2458,7 +4769,6 @@
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
-      <c r="N26" s="1"/>
       <c r="O26" s="1">
         <v>1</v>
       </c>
@@ -2468,7 +4778,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="C27" s="9">
         <v>150</v>
@@ -2488,7 +4798,6 @@
       <c r="H27" s="1">
         <v>58</v>
       </c>
-      <c r="I27" s="1"/>
       <c r="J27" s="1">
         <v>2</v>
       </c>
@@ -2497,7 +4806,6 @@
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="1"/>
       <c r="O27" s="1">
         <v>1</v>
       </c>
@@ -2507,7 +4815,7 @@
         <v>17001</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>72</v>
+        <v>139</v>
       </c>
       <c r="C28" s="9">
         <v>150</v>
@@ -2527,7 +4835,6 @@
       <c r="H28" s="1">
         <v>144</v>
       </c>
-      <c r="I28" s="1"/>
       <c r="J28" s="1">
         <v>2</v>
       </c>
@@ -2536,7 +4843,6 @@
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="1"/>
       <c r="O28" s="1">
         <v>1</v>
       </c>
@@ -2546,7 +4852,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="C29" s="1">
         <v>200</v>
@@ -2577,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="C30" s="1">
         <v>200</v>
@@ -2608,7 +4914,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="C31" s="9">
         <v>220</v>
@@ -2628,14 +4934,11 @@
       <c r="H31" s="1">
         <v>20</v>
       </c>
-      <c r="I31" s="1"/>
       <c r="J31" s="1">
         <v>2</v>
       </c>
-      <c r="K31" s="1"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="1"/>
       <c r="O31" s="1">
         <v>1</v>
       </c>
@@ -2645,7 +4948,7 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="C32" s="9">
         <v>250</v>
@@ -2662,7 +4965,6 @@
       <c r="H32" s="1">
         <v>215</v>
       </c>
-      <c r="I32" s="1"/>
       <c r="J32" s="1">
         <v>2</v>
       </c>
@@ -2671,7 +4973,6 @@
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
-      <c r="N32" s="1"/>
       <c r="O32" s="1">
         <v>1</v>
       </c>
@@ -2681,7 +4982,7 @@
         <v>24001</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="C33" s="9">
         <v>250</v>
@@ -2698,7 +4999,6 @@
       <c r="H33" s="1">
         <v>38</v>
       </c>
-      <c r="I33" s="1"/>
       <c r="J33" s="1">
         <v>2</v>
       </c>
@@ -2707,7 +5007,6 @@
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
-      <c r="N33" s="1"/>
       <c r="O33" s="1">
         <v>1</v>
       </c>
@@ -2717,7 +5016,7 @@
         <v>26</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C34" s="9">
         <v>300</v>
@@ -2737,7 +5036,6 @@
       <c r="H34" s="1">
         <v>105</v>
       </c>
-      <c r="I34" s="1"/>
       <c r="J34" s="1">
         <v>2</v>
       </c>
@@ -2746,7 +5044,6 @@
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
-      <c r="N34" s="1"/>
       <c r="O34" s="1">
         <v>1</v>
       </c>
@@ -2756,7 +5053,7 @@
         <v>2601</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="C35" s="9">
         <v>300</v>
@@ -2793,7 +5090,7 @@
         <v>28</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="C36" s="9">
         <v>330</v>
@@ -2813,7 +5110,6 @@
       <c r="H36" s="1">
         <v>205</v>
       </c>
-      <c r="I36" s="1"/>
       <c r="J36" s="1">
         <v>2</v>
       </c>
@@ -2822,7 +5118,6 @@
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
-      <c r="N36" s="1"/>
       <c r="O36" s="1">
         <v>1</v>
       </c>
@@ -2832,7 +5127,7 @@
         <v>2801</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="C37" s="9">
         <v>330</v>
@@ -2869,7 +5164,7 @@
         <v>2802</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="C38" s="9">
         <v>330</v>
@@ -2906,7 +5201,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="C39" s="1">
         <v>350</v>
@@ -2931,7 +5226,6 @@
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-      <c r="N39" s="1"/>
       <c r="O39" s="1">
         <v>1</v>
       </c>
@@ -2941,7 +5235,7 @@
         <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
@@ -2973,7 +5267,7 @@
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -3005,7 +5299,7 @@
         <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
@@ -3037,7 +5331,7 @@
         <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
@@ -3069,7 +5363,7 @@
         <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -3101,7 +5395,7 @@
         <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
@@ -3133,7 +5427,7 @@
         <v>54</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="D46" s="5">
         <v>1</v>
@@ -3165,7 +5459,7 @@
         <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D47" s="5">
         <v>1</v>
@@ -3197,7 +5491,7 @@
         <v>16001</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -3229,7 +5523,7 @@
         <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -3259,7 +5553,7 @@
         <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="C50" s="1">
         <v>70</v>
@@ -3274,7 +5568,6 @@
       <c r="H50" s="1">
         <v>80</v>
       </c>
-      <c r="I50"/>
       <c r="J50" s="1">
         <v>2</v>
       </c>
@@ -3287,7 +5580,7 @@
         <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>98</v>
@@ -3325,7 +5618,7 @@
         <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="C52" s="11">
         <v>400</v>
@@ -3355,7 +5648,7 @@
         <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="C53" s="11">
         <v>500</v>
@@ -3385,7 +5678,7 @@
         <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="C54" s="11">
         <v>300</v>
@@ -3415,7 +5708,7 @@
         <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>98</v>
@@ -3454,7 +5747,7 @@
         <v>70001</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>98</v>
@@ -3493,7 +5786,7 @@
         <v>70002</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>98</v>
@@ -3529,57 +5822,56 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A23">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A26">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28:A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49:A50">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A47 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A48 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A37 A39:A48 A51:A55 A58:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A57">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25:A26">
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28:A30">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49:A50">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A37 A39:A48 A51:A55 A58:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A48 A51:A55 A58:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A14 A17 A24 A27 A31:A32 A34:A37 A39:A47 A51:A55 A58:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>